--- a/backend/export.xlsx
+++ b/backend/export.xlsx
@@ -432,7 +432,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>kanak</v>
+        <v>kanak sharma</v>
       </c>
       <c r="C3" t="str">
         <v>8888888888</v>
